--- a/Exp3_PTO_GRPO/eda/results/arms/validity/tables/gpt-4o-mini/validity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/validity/tables/gpt-4o-mini/validity.xlsx
@@ -2729,7 +2729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,34 +3343,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>300.568</v>
+        <v>698.408</v>
       </c>
       <c r="F19" t="n">
-        <v>0.93</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>28.385</v>
+        <v>28.802</v>
       </c>
       <c r="I19" t="n">
-        <v>14.333</v>
+        <v>14.427</v>
       </c>
     </row>
     <row r="20">
@@ -3388,22 +3388,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>285.074</v>
+        <v>300.568</v>
       </c>
       <c r="F20" t="n">
-        <v>0.844</v>
+        <v>0.93</v>
       </c>
       <c r="G20" t="n">
-        <v>0.375</v>
+        <v>0.49</v>
       </c>
       <c r="H20" t="n">
-        <v>25.896</v>
+        <v>28.385</v>
       </c>
       <c r="I20" t="n">
-        <v>13.01</v>
+        <v>14.333</v>
       </c>
     </row>
     <row r="21">
@@ -3421,22 +3421,22 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>310.382</v>
+        <v>285.074</v>
       </c>
       <c r="F21" t="n">
-        <v>0.779</v>
+        <v>0.844</v>
       </c>
       <c r="G21" t="n">
-        <v>0.271</v>
+        <v>0.375</v>
       </c>
       <c r="H21" t="n">
-        <v>27.688</v>
+        <v>25.896</v>
       </c>
       <c r="I21" t="n">
-        <v>13.917</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="22">
@@ -3454,22 +3454,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>352.748</v>
+        <v>310.382</v>
       </c>
       <c r="F22" t="n">
-        <v>0.856</v>
+        <v>0.779</v>
       </c>
       <c r="G22" t="n">
-        <v>0.104</v>
+        <v>0.271</v>
       </c>
       <c r="H22" t="n">
-        <v>23.927</v>
+        <v>27.688</v>
       </c>
       <c r="I22" t="n">
-        <v>12.01</v>
+        <v>13.917</v>
       </c>
     </row>
     <row r="23">
@@ -3487,22 +3487,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>394.514</v>
+        <v>352.748</v>
       </c>
       <c r="F23" t="n">
-        <v>0.752</v>
+        <v>0.856</v>
       </c>
       <c r="G23" t="n">
-        <v>0.042</v>
+        <v>0.104</v>
       </c>
       <c r="H23" t="n">
-        <v>23.854</v>
+        <v>23.927</v>
       </c>
       <c r="I23" t="n">
-        <v>11.948</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="24">
@@ -3520,22 +3520,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>482.772</v>
+        <v>394.514</v>
       </c>
       <c r="F24" t="n">
-        <v>0.804</v>
+        <v>0.752</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01</v>
+        <v>0.042</v>
       </c>
       <c r="H24" t="n">
-        <v>23.188</v>
+        <v>23.854</v>
       </c>
       <c r="I24" t="n">
-        <v>11.604</v>
+        <v>11.948</v>
       </c>
     </row>
     <row r="25">
@@ -3553,22 +3553,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>553.494</v>
+        <v>482.772</v>
       </c>
       <c r="F25" t="n">
-        <v>0.742</v>
+        <v>0.804</v>
       </c>
       <c r="G25" t="n">
         <v>0.01</v>
       </c>
       <c r="H25" t="n">
-        <v>21.719</v>
+        <v>23.188</v>
       </c>
       <c r="I25" t="n">
-        <v>10.885</v>
+        <v>11.604</v>
       </c>
     </row>
     <row r="26">
@@ -3586,22 +3586,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>574.405</v>
+        <v>553.494</v>
       </c>
       <c r="F26" t="n">
-        <v>0.68</v>
+        <v>0.742</v>
       </c>
       <c r="G26" t="n">
         <v>0.01</v>
       </c>
       <c r="H26" t="n">
-        <v>22.719</v>
+        <v>21.719</v>
       </c>
       <c r="I26" t="n">
-        <v>11.385</v>
+        <v>10.885</v>
       </c>
     </row>
     <row r="27">
@@ -3619,22 +3619,22 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>641.316</v>
+        <v>574.405</v>
       </c>
       <c r="F27" t="n">
-        <v>0.675</v>
+        <v>0.68</v>
       </c>
       <c r="G27" t="n">
         <v>0.01</v>
       </c>
       <c r="H27" t="n">
-        <v>20.771</v>
+        <v>22.719</v>
       </c>
       <c r="I27" t="n">
-        <v>10.406</v>
+        <v>11.385</v>
       </c>
     </row>
     <row r="28">
@@ -3652,22 +3652,22 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>641.712</v>
+        <v>641.316</v>
       </c>
       <c r="F28" t="n">
-        <v>0.647</v>
+        <v>0.675</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H28" t="n">
-        <v>19.198</v>
+        <v>20.771</v>
       </c>
       <c r="I28" t="n">
-        <v>9.646000000000001</v>
+        <v>10.406</v>
       </c>
     </row>
     <row r="29">
@@ -3685,28 +3685,28 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>686.202</v>
+        <v>641.712</v>
       </c>
       <c r="F29" t="n">
-        <v>0.55</v>
+        <v>0.647</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>20.385</v>
+        <v>19.198</v>
       </c>
       <c r="I29" t="n">
-        <v>10.229</v>
+        <v>9.646000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3715,25 +3715,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>274.884</v>
+        <v>686.202</v>
       </c>
       <c r="F30" t="n">
-        <v>0.766</v>
+        <v>0.55</v>
       </c>
       <c r="G30" t="n">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>30.49</v>
+        <v>20.385</v>
       </c>
       <c r="I30" t="n">
-        <v>15.302</v>
+        <v>10.229</v>
       </c>
     </row>
     <row r="31">
@@ -3751,22 +3751,22 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>288.916</v>
+        <v>274.884</v>
       </c>
       <c r="F31" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="G31" t="n">
-        <v>0.427</v>
+        <v>0.448</v>
       </c>
       <c r="H31" t="n">
-        <v>26.323</v>
+        <v>30.49</v>
       </c>
       <c r="I31" t="n">
-        <v>13.24</v>
+        <v>15.302</v>
       </c>
     </row>
     <row r="32">
@@ -3784,22 +3784,22 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>366.031</v>
+        <v>288.916</v>
       </c>
       <c r="F32" t="n">
-        <v>0.779</v>
+        <v>0.767</v>
       </c>
       <c r="G32" t="n">
-        <v>0.417</v>
+        <v>0.427</v>
       </c>
       <c r="H32" t="n">
-        <v>26.615</v>
+        <v>26.323</v>
       </c>
       <c r="I32" t="n">
-        <v>13.396</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="33">
@@ -3817,22 +3817,22 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>421.129</v>
+        <v>366.031</v>
       </c>
       <c r="F33" t="n">
-        <v>0.823</v>
+        <v>0.779</v>
       </c>
       <c r="G33" t="n">
-        <v>0.219</v>
+        <v>0.417</v>
       </c>
       <c r="H33" t="n">
-        <v>25.49</v>
+        <v>26.615</v>
       </c>
       <c r="I33" t="n">
-        <v>12.812</v>
+        <v>13.396</v>
       </c>
     </row>
     <row r="34">
@@ -3850,22 +3850,22 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>482.746</v>
+        <v>421.129</v>
       </c>
       <c r="F34" t="n">
-        <v>0.766</v>
+        <v>0.823</v>
       </c>
       <c r="G34" t="n">
-        <v>0.115</v>
+        <v>0.219</v>
       </c>
       <c r="H34" t="n">
-        <v>22.844</v>
+        <v>25.49</v>
       </c>
       <c r="I34" t="n">
-        <v>11.458</v>
+        <v>12.812</v>
       </c>
     </row>
     <row r="35">
@@ -3883,22 +3883,22 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>584.5410000000001</v>
+        <v>482.746</v>
       </c>
       <c r="F35" t="n">
-        <v>0.715</v>
+        <v>0.766</v>
       </c>
       <c r="G35" t="n">
-        <v>0.042</v>
+        <v>0.115</v>
       </c>
       <c r="H35" t="n">
-        <v>23.719</v>
+        <v>22.844</v>
       </c>
       <c r="I35" t="n">
-        <v>11.896</v>
+        <v>11.458</v>
       </c>
     </row>
     <row r="36">
@@ -3916,22 +3916,22 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>618.345</v>
+        <v>584.5410000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="G36" t="n">
-        <v>0.083</v>
+        <v>0.042</v>
       </c>
       <c r="H36" t="n">
-        <v>25.26</v>
+        <v>23.719</v>
       </c>
       <c r="I36" t="n">
-        <v>12.677</v>
+        <v>11.896</v>
       </c>
     </row>
     <row r="37">
@@ -3949,22 +3949,22 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>716.595</v>
+        <v>618.345</v>
       </c>
       <c r="F37" t="n">
-        <v>0.595</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01</v>
+        <v>0.083</v>
       </c>
       <c r="H37" t="n">
-        <v>23.302</v>
+        <v>25.26</v>
       </c>
       <c r="I37" t="n">
-        <v>11.677</v>
+        <v>12.677</v>
       </c>
     </row>
     <row r="38">
@@ -3982,22 +3982,22 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>730.672</v>
+        <v>716.595</v>
       </c>
       <c r="F38" t="n">
-        <v>0.681</v>
+        <v>0.595</v>
       </c>
       <c r="G38" t="n">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
       <c r="H38" t="n">
-        <v>25.646</v>
+        <v>23.302</v>
       </c>
       <c r="I38" t="n">
-        <v>12.844</v>
+        <v>11.677</v>
       </c>
     </row>
     <row r="39">
@@ -4015,22 +4015,22 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>801.897</v>
+        <v>730.672</v>
       </c>
       <c r="F39" t="n">
-        <v>0.589</v>
+        <v>0.681</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="H39" t="n">
-        <v>27.49</v>
+        <v>25.646</v>
       </c>
       <c r="I39" t="n">
-        <v>13.771</v>
+        <v>12.844</v>
       </c>
     </row>
     <row r="40">
@@ -4048,21 +4048,54 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>801.897</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="I40" t="n">
+        <v>13.771</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
         <v>10</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E41" t="n">
         <v>810.875</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>0.616</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G41" t="n">
         <v>0.01</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H41" t="n">
         <v>28.698</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I41" t="n">
         <v>14.385</v>
       </c>
     </row>
@@ -4125,10 +4158,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C3" t="n">
-        <v>456</v>
+        <v>537</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>

--- a/Exp3_PTO_GRPO/eda/results/arms/validity/tables/gpt-4o-mini/validity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/validity/tables/gpt-4o-mini/validity.xlsx
@@ -506,7 +506,7 @@
         <v>55.2</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="E2" t="n">
         <v>0.405</v>
@@ -521,19 +521,19 @@
         <v>0.417</v>
       </c>
       <c r="I2" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="J2" t="n">
         <v>0.399</v>
       </c>
       <c r="K2" t="n">
-        <v>0.052</v>
+        <v>0.049</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.049</v>
+        <v>-0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="N2" t="n">
         <v>-0.101</v>
@@ -595,40 +595,40 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>56.1</v>
+        <v>55.8</v>
       </c>
       <c r="D4" t="n">
-        <v>17.5</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.406</v>
+        <v>0.407</v>
       </c>
       <c r="F4" t="n">
-        <v>0.406</v>
+        <v>0.407</v>
       </c>
       <c r="G4" t="n">
         <v>0.409</v>
       </c>
       <c r="H4" t="n">
-        <v>0.415</v>
+        <v>0.416</v>
       </c>
       <c r="I4" t="n">
-        <v>0.393</v>
+        <v>0.391</v>
       </c>
       <c r="J4" t="n">
-        <v>0.395</v>
+        <v>0.398</v>
       </c>
       <c r="K4" t="n">
-        <v>0.022</v>
+        <v>0.015</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.074</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.066</v>
+        <v>0.05</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.102</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="5">
@@ -733,7 +733,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>91.3</v>
+        <v>91.2</v>
       </c>
       <c r="D7" t="n">
         <v>5.7</v>
@@ -751,7 +751,7 @@
         <v>0.457</v>
       </c>
       <c r="I7" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
     </row>
   </sheetData>
@@ -765,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,16 @@
           <t>q_per_turn_miti</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>q_turn_rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>q_per_q_turn</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -823,6 +833,12 @@
       <c r="F2" t="n">
         <v>0.4464</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.6486</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.2441</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -847,6 +863,12 @@
       <c r="F3" t="n">
         <v>0.4584</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.2337</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -871,6 +893,12 @@
       <c r="F4" t="n">
         <v>0.4233</v>
       </c>
+      <c r="G4" t="n">
+        <v>0.6575</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.169</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -895,6 +923,12 @@
       <c r="F5" t="n">
         <v>0.4017</v>
       </c>
+      <c r="G5" t="n">
+        <v>0.5063</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.4048</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -919,6 +953,12 @@
       <c r="F6" t="n">
         <v>0.3742</v>
       </c>
+      <c r="G6" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.3341</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -943,6 +983,12 @@
       <c r="F7" t="n">
         <v>0.3606</v>
       </c>
+      <c r="G7" t="n">
+        <v>0.2198</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.3689</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -967,6 +1013,12 @@
       <c r="F8" t="n">
         <v>0.3528</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.1938</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.2967</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -991,6 +1043,12 @@
       <c r="F9" t="n">
         <v>0.3542</v>
       </c>
+      <c r="G9" t="n">
+        <v>0.1695</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.2635</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1015,6 +1073,12 @@
       <c r="F10" t="n">
         <v>0.3426</v>
       </c>
+      <c r="G10" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.1788</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1039,6 +1103,12 @@
       <c r="F11" t="n">
         <v>0.3475</v>
       </c>
+      <c r="G11" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.1311</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1063,6 +1133,12 @@
       <c r="F12" t="n">
         <v>0.3193</v>
       </c>
+      <c r="G12" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.1406</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1087,6 +1163,12 @@
       <c r="F13" t="n">
         <v>0.4709</v>
       </c>
+      <c r="G13" t="n">
+        <v>0.5782</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.2823</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1111,6 +1193,12 @@
       <c r="F14" t="n">
         <v>0.4608</v>
       </c>
+      <c r="G14" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.3663</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1135,6 +1223,12 @@
       <c r="F15" t="n">
         <v>0.3976</v>
       </c>
+      <c r="G15" t="n">
+        <v>0.5944</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.3002</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1159,6 +1253,12 @@
       <c r="F16" t="n">
         <v>0.3988</v>
       </c>
+      <c r="G16" t="n">
+        <v>0.4942</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.3987</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1183,6 +1283,12 @@
       <c r="F17" t="n">
         <v>0.4006</v>
       </c>
+      <c r="G17" t="n">
+        <v>0.5031</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.5276</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1207,29 +1313,41 @@
       <c r="F18" t="n">
         <v>0.3839</v>
       </c>
+      <c r="G18" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.646</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4846</v>
+        <v>0.3724</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.7076</v>
       </c>
     </row>
     <row r="20">
@@ -1247,13 +1365,19 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8436</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4795</v>
+        <v>0.4846</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6687</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.3662</v>
       </c>
     </row>
     <row r="21">
@@ -1271,13 +1395,19 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7789</v>
+        <v>0.8436</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4513</v>
+        <v>0.4795</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.3253</v>
       </c>
     </row>
     <row r="22">
@@ -1295,13 +1425,19 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8562</v>
+        <v>0.7789</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4805</v>
+        <v>0.4513</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.6258</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.277</v>
       </c>
     </row>
     <row r="23">
@@ -1319,13 +1455,19 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.752</v>
+        <v>0.8562</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4507</v>
+        <v>0.4805</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.4615</v>
       </c>
     </row>
     <row r="24">
@@ -1343,13 +1485,19 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4459</v>
+        <v>0.4507</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.4953</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.5419</v>
       </c>
     </row>
     <row r="25">
@@ -1367,13 +1515,19 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7415</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4976</v>
+        <v>0.4459</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.4954</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.6112</v>
       </c>
     </row>
     <row r="26">
@@ -1391,13 +1545,19 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6803</v>
+        <v>0.7415</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4419</v>
+        <v>0.4976</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.762</v>
       </c>
     </row>
     <row r="27">
@@ -1415,13 +1575,19 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6803</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4058</v>
+        <v>0.4419</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.6697</v>
       </c>
     </row>
     <row r="28">
@@ -1439,13 +1605,19 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6472</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3937</v>
+        <v>0.4058</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.7641</v>
       </c>
     </row>
     <row r="29">
@@ -1463,19 +1635,25 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5501</v>
+        <v>0.6472</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4048</v>
+        <v>0.3937</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.6455</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1484,16 +1662,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7659</v>
+        <v>0.5501</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4765</v>
+        <v>0.4048</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.6704</v>
       </c>
     </row>
     <row r="31">
@@ -1511,13 +1695,19 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7668</v>
+        <v>0.7659</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4864</v>
+        <v>0.4765</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.6159</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.2255</v>
       </c>
     </row>
     <row r="32">
@@ -1535,13 +1725,19 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.779</v>
+        <v>0.7668</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4232</v>
+        <v>0.4864</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.2056</v>
       </c>
     </row>
     <row r="33">
@@ -1559,13 +1755,19 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8226</v>
+        <v>0.779</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4543</v>
+        <v>0.4232</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.3339</v>
       </c>
     </row>
     <row r="34">
@@ -1583,13 +1785,19 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7663</v>
+        <v>0.8226</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4444</v>
+        <v>0.4543</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.5684</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.4624</v>
       </c>
     </row>
     <row r="35">
@@ -1607,13 +1815,19 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7155</v>
+        <v>0.7663</v>
       </c>
       <c r="F35" t="n">
-        <v>0.437</v>
+        <v>0.4444</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.4863</v>
       </c>
     </row>
     <row r="36">
@@ -1631,13 +1845,19 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9429</v>
+        <v>0.7155</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4158</v>
+        <v>0.437</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.5633</v>
       </c>
     </row>
     <row r="37">
@@ -1655,13 +1875,19 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5954</v>
+        <v>0.9429</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4089</v>
+        <v>0.4158</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.8122</v>
       </c>
     </row>
     <row r="38">
@@ -1679,13 +1905,19 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6808</v>
+        <v>0.5954</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3931</v>
+        <v>0.4089</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.4731</v>
       </c>
     </row>
     <row r="39">
@@ -1703,13 +1935,19 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5888</v>
+        <v>0.6808</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3837</v>
+        <v>0.3931</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.5895</v>
       </c>
     </row>
     <row r="40">
@@ -1727,13 +1965,49 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5888</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.5308</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
         <v>10</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E41" t="n">
         <v>0.6156</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>0.3762</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.4297</v>
       </c>
     </row>
   </sheetData>
@@ -1747,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2193,25 +2467,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0025</v>
+        <v>0.0216</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0129</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="20">
@@ -2229,13 +2503,13 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0009</v>
+        <v>0.0025</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0293</v>
+        <v>0.0129</v>
       </c>
     </row>
     <row r="21">
@@ -2253,13 +2527,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0167</v>
+        <v>0.0293</v>
       </c>
     </row>
     <row r="22">
@@ -2277,13 +2551,13 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0261</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="23">
@@ -2301,13 +2575,13 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0339</v>
+        <v>0.0261</v>
       </c>
     </row>
     <row r="24">
@@ -2325,13 +2599,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0091</v>
+        <v>0.0023</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0373</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="25">
@@ -2349,13 +2623,13 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0229</v>
+        <v>0.0091</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0775</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="26">
@@ -2373,13 +2647,13 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0702</v>
+        <v>0.0229</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1288</v>
+        <v>0.0775</v>
       </c>
     </row>
     <row r="27">
@@ -2397,13 +2671,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="F27" t="n">
-        <v>0.154</v>
+        <v>0.1288</v>
       </c>
     </row>
     <row r="28">
@@ -2421,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1896</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2702</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="29">
@@ -2445,19 +2719,19 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2096</v>
+        <v>0.1896</v>
       </c>
       <c r="F29" t="n">
-        <v>0.299</v>
+        <v>0.2702</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2466,16 +2740,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.2096</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0081</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="31">
@@ -2493,13 +2767,13 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0313</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="32">
@@ -2517,13 +2791,13 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.017</v>
+        <v>0.0313</v>
       </c>
     </row>
     <row r="33">
@@ -2541,13 +2815,13 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0283</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="34">
@@ -2565,13 +2839,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0014</v>
+        <v>0.0024</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0429</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="35">
@@ -2589,13 +2863,13 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0053</v>
+        <v>0.0014</v>
       </c>
       <c r="F35" t="n">
-        <v>0.034</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="36">
@@ -2613,13 +2887,13 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0103</v>
+        <v>0.0053</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0364</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="37">
@@ -2637,13 +2911,13 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0081</v>
+        <v>0.0103</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0329</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="38">
@@ -2661,13 +2935,13 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0204</v>
+        <v>0.0081</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0418</v>
+        <v>0.0329</v>
       </c>
     </row>
     <row r="39">
@@ -2685,13 +2959,13 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0308</v>
+        <v>0.0204</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0407</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="40">
@@ -2709,12 +2983,36 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0407</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
         <v>10</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E41" t="n">
         <v>0.0452</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>0.0432</v>
       </c>
     </row>
@@ -2729,7 +3027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2778,6 +3076,26 @@
           <t>n_th_turns</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>q_turn_rate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>q_per_q_turn</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>sents_per_turn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>q_per_sentence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2811,6 +3129,18 @@
       <c r="I2" t="n">
         <v>14.469</v>
       </c>
+      <c r="J2" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.184</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.231</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2844,6 +3174,18 @@
       <c r="I3" t="n">
         <v>13</v>
       </c>
+      <c r="J3" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.192</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2877,6 +3219,18 @@
       <c r="I4" t="n">
         <v>15.667</v>
       </c>
+      <c r="J4" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.234</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2910,6 +3264,18 @@
       <c r="I5" t="n">
         <v>13.812</v>
       </c>
+      <c r="J5" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.366</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.171</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2943,6 +3309,18 @@
       <c r="I6" t="n">
         <v>15.271</v>
       </c>
+      <c r="J6" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.843</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.099</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2976,6 +3354,18 @@
       <c r="I7" t="n">
         <v>15.344</v>
       </c>
+      <c r="J7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.741</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.057</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3009,6 +3399,18 @@
       <c r="I8" t="n">
         <v>16.177</v>
       </c>
+      <c r="J8" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.338</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.048</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3042,6 +3444,18 @@
       <c r="I9" t="n">
         <v>14.458</v>
       </c>
+      <c r="J9" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.912</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.033</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3075,6 +3489,18 @@
       <c r="I10" t="n">
         <v>12.135</v>
       </c>
+      <c r="J10" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8.661</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.027</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3108,6 +3534,18 @@
       <c r="I11" t="n">
         <v>19.052</v>
       </c>
+      <c r="J11" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.032</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3141,6 +3579,18 @@
       <c r="I12" t="n">
         <v>12.75</v>
       </c>
+      <c r="J12" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.548</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.014</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3174,6 +3624,18 @@
       <c r="I13" t="n">
         <v>14.24</v>
       </c>
+      <c r="J13" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.338</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.196</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3207,6 +3669,18 @@
       <c r="I14" t="n">
         <v>14.146</v>
       </c>
+      <c r="J14" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.491</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.222</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3240,6 +3714,18 @@
       <c r="I15" t="n">
         <v>14.948</v>
       </c>
+      <c r="J15" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.346</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.208</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3273,6 +3759,18 @@
       <c r="I16" t="n">
         <v>14.562</v>
       </c>
+      <c r="J16" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5.254</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.153</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3306,6 +3804,18 @@
       <c r="I17" t="n">
         <v>12.896</v>
       </c>
+      <c r="J17" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5.514</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.151</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3339,6 +3849,18 @@
       <c r="I18" t="n">
         <v>11.312</v>
       </c>
+      <c r="J18" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7.378</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.096</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3372,71 +3894,107 @@
       <c r="I19" t="n">
         <v>14.427</v>
       </c>
+      <c r="J19" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7.646</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.108</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>300.568</v>
+        <v>774.924</v>
       </c>
       <c r="F20" t="n">
-        <v>0.93</v>
+        <v>1.075</v>
       </c>
       <c r="G20" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>28.385</v>
+        <v>29.635</v>
       </c>
       <c r="I20" t="n">
-        <v>14.333</v>
+        <v>14.844</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.014</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7.987</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>285.074</v>
+        <v>839.508</v>
       </c>
       <c r="F21" t="n">
-        <v>0.844</v>
+        <v>1.142</v>
       </c>
       <c r="G21" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>25.896</v>
+        <v>32.646</v>
       </c>
       <c r="I21" t="n">
-        <v>13.01</v>
+        <v>16.354</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.153</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8.082000000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.144</v>
       </c>
     </row>
     <row r="22">
@@ -3454,22 +4012,34 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>310.382</v>
+        <v>300.568</v>
       </c>
       <c r="F22" t="n">
-        <v>0.779</v>
+        <v>0.93</v>
       </c>
       <c r="G22" t="n">
-        <v>0.271</v>
+        <v>0.49</v>
       </c>
       <c r="H22" t="n">
-        <v>27.688</v>
+        <v>28.385</v>
       </c>
       <c r="I22" t="n">
-        <v>13.917</v>
+        <v>14.333</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4.604</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.227</v>
       </c>
     </row>
     <row r="23">
@@ -3487,22 +4057,34 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>352.748</v>
+        <v>285.074</v>
       </c>
       <c r="F23" t="n">
-        <v>0.856</v>
+        <v>0.844</v>
       </c>
       <c r="G23" t="n">
-        <v>0.104</v>
+        <v>0.375</v>
       </c>
       <c r="H23" t="n">
-        <v>23.927</v>
+        <v>25.896</v>
       </c>
       <c r="I23" t="n">
-        <v>12.01</v>
+        <v>13.01</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.221</v>
       </c>
     </row>
     <row r="24">
@@ -3520,22 +4102,34 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>394.514</v>
+        <v>310.382</v>
       </c>
       <c r="F24" t="n">
-        <v>0.752</v>
+        <v>0.779</v>
       </c>
       <c r="G24" t="n">
-        <v>0.042</v>
+        <v>0.271</v>
       </c>
       <c r="H24" t="n">
-        <v>23.854</v>
+        <v>27.688</v>
       </c>
       <c r="I24" t="n">
-        <v>11.948</v>
+        <v>13.917</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.351</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.209</v>
       </c>
     </row>
     <row r="25">
@@ -3553,22 +4147,34 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>482.772</v>
+        <v>352.748</v>
       </c>
       <c r="F25" t="n">
-        <v>0.804</v>
+        <v>0.856</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01</v>
+        <v>0.104</v>
       </c>
       <c r="H25" t="n">
-        <v>23.188</v>
+        <v>23.927</v>
       </c>
       <c r="I25" t="n">
-        <v>11.604</v>
+        <v>12.01</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.917</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.192</v>
       </c>
     </row>
     <row r="26">
@@ -3586,22 +4192,34 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>553.494</v>
+        <v>394.514</v>
       </c>
       <c r="F26" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01</v>
+        <v>0.042</v>
       </c>
       <c r="H26" t="n">
-        <v>21.719</v>
+        <v>23.854</v>
       </c>
       <c r="I26" t="n">
-        <v>10.885</v>
+        <v>11.948</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="L26" t="n">
+        <v>5.347</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.162</v>
       </c>
     </row>
     <row r="27">
@@ -3619,22 +4237,34 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>574.405</v>
+        <v>482.772</v>
       </c>
       <c r="F27" t="n">
-        <v>0.68</v>
+        <v>0.804</v>
       </c>
       <c r="G27" t="n">
         <v>0.01</v>
       </c>
       <c r="H27" t="n">
-        <v>22.719</v>
+        <v>23.188</v>
       </c>
       <c r="I27" t="n">
-        <v>11.385</v>
+        <v>11.604</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.611</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6.165</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.148</v>
       </c>
     </row>
     <row r="28">
@@ -3652,22 +4282,34 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>641.316</v>
+        <v>553.494</v>
       </c>
       <c r="F28" t="n">
-        <v>0.675</v>
+        <v>0.742</v>
       </c>
       <c r="G28" t="n">
         <v>0.01</v>
       </c>
       <c r="H28" t="n">
-        <v>20.771</v>
+        <v>21.719</v>
       </c>
       <c r="I28" t="n">
-        <v>10.406</v>
+        <v>10.885</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="L28" t="n">
+        <v>7.569</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.112</v>
       </c>
     </row>
     <row r="29">
@@ -3685,22 +4327,34 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>641.712</v>
+        <v>574.405</v>
       </c>
       <c r="F29" t="n">
-        <v>0.647</v>
+        <v>0.68</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H29" t="n">
-        <v>19.198</v>
+        <v>22.719</v>
       </c>
       <c r="I29" t="n">
-        <v>9.646000000000001</v>
+        <v>11.385</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8.481999999999999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.098</v>
       </c>
     </row>
     <row r="30">
@@ -3718,28 +4372,40 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>686.202</v>
+        <v>641.316</v>
       </c>
       <c r="F30" t="n">
-        <v>0.55</v>
+        <v>0.675</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H30" t="n">
-        <v>20.385</v>
+        <v>20.771</v>
       </c>
       <c r="I30" t="n">
-        <v>10.229</v>
+        <v>10.406</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8.837999999999999</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.083</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3748,31 +4414,43 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>274.884</v>
+        <v>641.712</v>
       </c>
       <c r="F31" t="n">
-        <v>0.766</v>
+        <v>0.647</v>
       </c>
       <c r="G31" t="n">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>30.49</v>
+        <v>19.198</v>
       </c>
       <c r="I31" t="n">
-        <v>15.302</v>
+        <v>9.646000000000001</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9.657999999999999</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.078</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3781,25 +4459,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>288.916</v>
+        <v>686.202</v>
       </c>
       <c r="F32" t="n">
-        <v>0.767</v>
+        <v>0.55</v>
       </c>
       <c r="G32" t="n">
-        <v>0.427</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>26.323</v>
+        <v>20.385</v>
       </c>
       <c r="I32" t="n">
-        <v>13.24</v>
+        <v>10.229</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10.524</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="33">
@@ -3817,22 +4507,34 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>366.031</v>
+        <v>274.884</v>
       </c>
       <c r="F33" t="n">
-        <v>0.779</v>
+        <v>0.766</v>
       </c>
       <c r="G33" t="n">
-        <v>0.417</v>
+        <v>0.448</v>
       </c>
       <c r="H33" t="n">
-        <v>26.615</v>
+        <v>30.49</v>
       </c>
       <c r="I33" t="n">
-        <v>13.396</v>
+        <v>15.302</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4.265</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.221</v>
       </c>
     </row>
     <row r="34">
@@ -3850,22 +4552,34 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>421.129</v>
+        <v>288.916</v>
       </c>
       <c r="F34" t="n">
-        <v>0.823</v>
+        <v>0.767</v>
       </c>
       <c r="G34" t="n">
-        <v>0.219</v>
+        <v>0.427</v>
       </c>
       <c r="H34" t="n">
-        <v>25.49</v>
+        <v>26.323</v>
       </c>
       <c r="I34" t="n">
-        <v>12.812</v>
+        <v>13.24</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4.393</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.204</v>
       </c>
     </row>
     <row r="35">
@@ -3883,22 +4597,34 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>482.746</v>
+        <v>366.031</v>
       </c>
       <c r="F35" t="n">
-        <v>0.766</v>
+        <v>0.779</v>
       </c>
       <c r="G35" t="n">
-        <v>0.115</v>
+        <v>0.417</v>
       </c>
       <c r="H35" t="n">
-        <v>22.844</v>
+        <v>26.615</v>
       </c>
       <c r="I35" t="n">
-        <v>11.458</v>
+        <v>13.396</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.103</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.194</v>
       </c>
     </row>
     <row r="36">
@@ -3916,22 +4642,34 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>584.5410000000001</v>
+        <v>421.129</v>
       </c>
       <c r="F36" t="n">
-        <v>0.715</v>
+        <v>0.823</v>
       </c>
       <c r="G36" t="n">
-        <v>0.042</v>
+        <v>0.219</v>
       </c>
       <c r="H36" t="n">
-        <v>23.719</v>
+        <v>25.49</v>
       </c>
       <c r="I36" t="n">
-        <v>11.896</v>
+        <v>12.812</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5.563</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.173</v>
       </c>
     </row>
     <row r="37">
@@ -3949,22 +4687,34 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>618.345</v>
+        <v>482.746</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.766</v>
       </c>
       <c r="G37" t="n">
-        <v>0.083</v>
+        <v>0.115</v>
       </c>
       <c r="H37" t="n">
-        <v>25.26</v>
+        <v>22.844</v>
       </c>
       <c r="I37" t="n">
-        <v>12.677</v>
+        <v>11.458</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.486</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.282</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.138</v>
       </c>
     </row>
     <row r="38">
@@ -3982,22 +4732,34 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>716.595</v>
+        <v>584.5410000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>0.595</v>
+        <v>0.715</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01</v>
+        <v>0.042</v>
       </c>
       <c r="H38" t="n">
-        <v>23.302</v>
+        <v>23.719</v>
       </c>
       <c r="I38" t="n">
-        <v>11.677</v>
+        <v>11.896</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.563</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7.119</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.118</v>
       </c>
     </row>
     <row r="39">
@@ -4015,22 +4777,34 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>730.672</v>
+        <v>618.345</v>
       </c>
       <c r="F39" t="n">
-        <v>0.681</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>0.021</v>
+        <v>0.083</v>
       </c>
       <c r="H39" t="n">
-        <v>25.646</v>
+        <v>25.26</v>
       </c>
       <c r="I39" t="n">
-        <v>12.844</v>
+        <v>12.677</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7.575</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="40">
@@ -4048,22 +4822,34 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>801.897</v>
+        <v>716.595</v>
       </c>
       <c r="F40" t="n">
-        <v>0.589</v>
+        <v>0.595</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>27.49</v>
+        <v>23.302</v>
       </c>
       <c r="I40" t="n">
-        <v>13.771</v>
+        <v>11.677</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8.215</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -4081,22 +4867,124 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" t="n">
+        <v>730.672</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H41" t="n">
+        <v>25.646</v>
+      </c>
+      <c r="I41" t="n">
+        <v>12.844</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.589</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8.754</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>9</v>
+      </c>
+      <c r="E42" t="n">
+        <v>801.897</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13.771</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="L42" t="n">
+        <v>8.962</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
         <v>10</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E43" t="n">
         <v>810.875</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F43" t="n">
         <v>0.616</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G43" t="n">
         <v>0.01</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H43" t="n">
         <v>28.698</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I43" t="n">
         <v>14.385</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.081</v>
       </c>
     </row>
   </sheetData>
@@ -4158,10 +5046,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="C3" t="n">
-        <v>537</v>
+        <v>684</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>

--- a/Exp3_PTO_GRPO/eda/results/arms/validity/tables/gpt-4o-mini/validity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/validity/tables/gpt-4o-mini/validity.xlsx
@@ -503,40 +503,40 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="D2" t="n">
-        <v>17.1</v>
+        <v>17.7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.405</v>
+        <v>0.407</v>
       </c>
       <c r="F2" t="n">
-        <v>0.41</v>
+        <v>0.411</v>
       </c>
       <c r="G2" t="n">
-        <v>0.411</v>
+        <v>0.412</v>
       </c>
       <c r="H2" t="n">
-        <v>0.417</v>
+        <v>0.418</v>
       </c>
       <c r="I2" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="J2" t="n">
-        <v>0.399</v>
+        <v>0.402</v>
       </c>
       <c r="K2" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.049</v>
       </c>
-      <c r="L2" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.037</v>
-      </c>
       <c r="N2" t="n">
-        <v>-0.101</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="3">
@@ -595,40 +595,40 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>55.8</v>
+        <v>54.8</v>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.407</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.409</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.416</v>
+        <v>0.417</v>
       </c>
       <c r="I4" t="n">
-        <v>0.391</v>
+        <v>0.388</v>
       </c>
       <c r="J4" t="n">
-        <v>0.398</v>
+        <v>0.405</v>
       </c>
       <c r="K4" t="n">
-        <v>0.015</v>
+        <v>-0.044</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05</v>
+        <v>0.093</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.099</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="5">
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>91.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="F7" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="G7" t="n">
         <v>0.451</v>
@@ -765,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1353,121 +1353,121 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9298999999999999</v>
+        <v>1.0746</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4846</v>
+        <v>0.3786</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6687</v>
+        <v>0.4811</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3662</v>
+        <v>2.0143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8436</v>
+        <v>1.1419</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4795</v>
+        <v>0.369</v>
       </c>
       <c r="G21" t="n">
-        <v>0.632</v>
+        <v>0.5024</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3253</v>
+        <v>2.1525</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7789</v>
+        <v>0.9028</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4513</v>
+        <v>0.3444</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6258</v>
+        <v>0.4683</v>
       </c>
       <c r="H22" t="n">
-        <v>1.277</v>
+        <v>1.8321</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8562</v>
+        <v>0.7189</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4805</v>
+        <v>0.3407</v>
       </c>
       <c r="G23" t="n">
-        <v>0.589</v>
+        <v>0.4055</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4615</v>
+        <v>1.7099</v>
       </c>
     </row>
     <row r="24">
@@ -1485,19 +1485,19 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.752</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4507</v>
+        <v>0.4846</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4953</v>
+        <v>0.6687</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5419</v>
+        <v>1.3662</v>
       </c>
     </row>
     <row r="25">
@@ -1515,19 +1515,19 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.8436</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4459</v>
+        <v>0.4795</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4954</v>
+        <v>0.632</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6112</v>
+        <v>1.3253</v>
       </c>
     </row>
     <row r="26">
@@ -1545,19 +1545,19 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7415</v>
+        <v>0.7789</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4976</v>
+        <v>0.4513</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4103</v>
+        <v>0.6258</v>
       </c>
       <c r="H26" t="n">
-        <v>1.762</v>
+        <v>1.277</v>
       </c>
     </row>
     <row r="27">
@@ -1575,19 +1575,19 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6803</v>
+        <v>0.8562</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4419</v>
+        <v>0.4805</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4061</v>
+        <v>0.589</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6697</v>
+        <v>1.4615</v>
       </c>
     </row>
     <row r="28">
@@ -1605,19 +1605,19 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.752</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4058</v>
+        <v>0.4507</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3891</v>
+        <v>0.4953</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7641</v>
+        <v>1.5419</v>
       </c>
     </row>
     <row r="29">
@@ -1635,19 +1635,19 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6472</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3937</v>
+        <v>0.4459</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3834</v>
+        <v>0.4954</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6455</v>
+        <v>1.6112</v>
       </c>
     </row>
     <row r="30">
@@ -1665,25 +1665,25 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5501</v>
+        <v>0.7415</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4048</v>
+        <v>0.4976</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3255</v>
+        <v>0.4103</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6704</v>
+        <v>1.762</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7659</v>
+        <v>0.6803</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4765</v>
+        <v>0.4419</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6159</v>
+        <v>0.4061</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2255</v>
+        <v>1.6697</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1722,28 +1722,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7668</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4864</v>
+        <v>0.4058</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6191</v>
+        <v>0.3891</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2056</v>
+        <v>1.7641</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1752,28 +1752,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>0.779</v>
+        <v>0.6472</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4232</v>
+        <v>0.3937</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5742</v>
+        <v>0.3834</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3339</v>
+        <v>1.6455</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1782,22 +1782,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8226</v>
+        <v>0.5501</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4543</v>
+        <v>0.4048</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5684</v>
+        <v>0.3255</v>
       </c>
       <c r="H34" t="n">
-        <v>1.4624</v>
+        <v>1.6704</v>
       </c>
     </row>
     <row r="35">
@@ -1815,19 +1815,19 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7663</v>
+        <v>0.7659</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4444</v>
+        <v>0.4765</v>
       </c>
       <c r="G35" t="n">
-        <v>0.49</v>
+        <v>0.6159</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4863</v>
+        <v>1.2255</v>
       </c>
     </row>
     <row r="36">
@@ -1845,19 +1845,19 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7155</v>
+        <v>0.7668</v>
       </c>
       <c r="F36" t="n">
-        <v>0.437</v>
+        <v>0.4864</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4439</v>
+        <v>0.6191</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5633</v>
+        <v>1.2056</v>
       </c>
     </row>
     <row r="37">
@@ -1875,19 +1875,19 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9429</v>
+        <v>0.779</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4158</v>
+        <v>0.4232</v>
       </c>
       <c r="G37" t="n">
-        <v>0.495</v>
+        <v>0.5742</v>
       </c>
       <c r="H37" t="n">
-        <v>1.8122</v>
+        <v>1.3339</v>
       </c>
     </row>
     <row r="38">
@@ -1905,19 +1905,19 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5954</v>
+        <v>0.8226</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4089</v>
+        <v>0.4543</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3874</v>
+        <v>0.5684</v>
       </c>
       <c r="H38" t="n">
-        <v>1.4731</v>
+        <v>1.4624</v>
       </c>
     </row>
     <row r="39">
@@ -1935,19 +1935,19 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6808</v>
+        <v>0.7663</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3931</v>
+        <v>0.4444</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4165</v>
+        <v>0.49</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5895</v>
+        <v>1.4863</v>
       </c>
     </row>
     <row r="40">
@@ -1965,19 +1965,19 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5888</v>
+        <v>0.7155</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3837</v>
+        <v>0.437</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3794</v>
+        <v>0.4439</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5308</v>
+        <v>1.5633</v>
       </c>
     </row>
     <row r="41">
@@ -1995,18 +1995,138 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9429</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.8122</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5954</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.4731</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6808</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.5895</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.5888</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.5308</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
         <v>10</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E45" t="n">
         <v>0.6156</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F45" t="n">
         <v>0.3762</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G45" t="n">
         <v>0.4188</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H45" t="n">
         <v>1.4297</v>
       </c>
     </row>
@@ -2021,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,97 +2611,97 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0025</v>
+        <v>0.0361</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0129</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0009</v>
+        <v>0.0382</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0293</v>
+        <v>0.0525</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.0589</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0167</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0012</v>
+        <v>0.0641</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0261</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="24">
@@ -2599,13 +2719,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0023</v>
+        <v>0.0025</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0339</v>
+        <v>0.0129</v>
       </c>
     </row>
     <row r="25">
@@ -2623,13 +2743,13 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0091</v>
+        <v>0.0009</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0373</v>
+        <v>0.0293</v>
       </c>
     </row>
     <row r="26">
@@ -2647,13 +2767,13 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0229</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0775</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="27">
@@ -2671,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0702</v>
+        <v>0.0012</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1288</v>
+        <v>0.0261</v>
       </c>
     </row>
     <row r="28">
@@ -2695,13 +2815,13 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0023</v>
       </c>
       <c r="F28" t="n">
-        <v>0.154</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="29">
@@ -2719,13 +2839,13 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1896</v>
+        <v>0.0091</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2702</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="30">
@@ -2743,19 +2863,19 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2096</v>
+        <v>0.0229</v>
       </c>
       <c r="F30" t="n">
-        <v>0.299</v>
+        <v>0.0775</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2764,22 +2884,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.0702</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0081</v>
+        <v>0.1288</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2788,22 +2908,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0313</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2812,22 +2932,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.1896</v>
       </c>
       <c r="F33" t="n">
-        <v>0.017</v>
+        <v>0.2702</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2836,16 +2956,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0024</v>
+        <v>0.2096</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0283</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="35">
@@ -2863,13 +2983,13 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0014</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0429</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="36">
@@ -2887,13 +3007,13 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0053</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.034</v>
+        <v>0.0313</v>
       </c>
     </row>
     <row r="37">
@@ -2911,13 +3031,13 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0364</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="38">
@@ -2935,13 +3055,13 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0081</v>
+        <v>0.0024</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0329</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="39">
@@ -2959,13 +3079,13 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0204</v>
+        <v>0.0014</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0418</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="40">
@@ -2983,13 +3103,13 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0308</v>
+        <v>0.0053</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0407</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="41">
@@ -3007,12 +3127,108 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0364</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0329</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0418</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0407</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
         <v>10</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E45" t="n">
         <v>0.0452</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F45" t="n">
         <v>0.0432</v>
       </c>
     </row>
@@ -3027,7 +3243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4000,91 +4216,91 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>300.568</v>
+        <v>856.164</v>
       </c>
       <c r="F22" t="n">
-        <v>0.93</v>
+        <v>0.903</v>
       </c>
       <c r="G22" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>28.385</v>
+        <v>33.667</v>
       </c>
       <c r="I22" t="n">
-        <v>14.333</v>
+        <v>16.854</v>
       </c>
       <c r="J22" t="n">
-        <v>0.669</v>
+        <v>0.468</v>
       </c>
       <c r="K22" t="n">
-        <v>1.366</v>
+        <v>1.832</v>
       </c>
       <c r="L22" t="n">
-        <v>4.604</v>
+        <v>8.4</v>
       </c>
       <c r="M22" t="n">
-        <v>0.227</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>285.074</v>
+        <v>849.274</v>
       </c>
       <c r="F23" t="n">
-        <v>0.844</v>
+        <v>0.719</v>
       </c>
       <c r="G23" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>25.896</v>
+        <v>31.896</v>
       </c>
       <c r="I23" t="n">
-        <v>13.01</v>
+        <v>15.969</v>
       </c>
       <c r="J23" t="n">
-        <v>0.632</v>
+        <v>0.406</v>
       </c>
       <c r="K23" t="n">
-        <v>1.325</v>
+        <v>1.71</v>
       </c>
       <c r="L23" t="n">
-        <v>4.27</v>
+        <v>8.894</v>
       </c>
       <c r="M23" t="n">
-        <v>0.221</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="24">
@@ -4102,34 +4318,34 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>310.382</v>
+        <v>300.568</v>
       </c>
       <c r="F24" t="n">
-        <v>0.779</v>
+        <v>0.93</v>
       </c>
       <c r="G24" t="n">
-        <v>0.271</v>
+        <v>0.49</v>
       </c>
       <c r="H24" t="n">
-        <v>27.688</v>
+        <v>28.385</v>
       </c>
       <c r="I24" t="n">
-        <v>13.917</v>
+        <v>14.333</v>
       </c>
       <c r="J24" t="n">
-        <v>0.626</v>
+        <v>0.669</v>
       </c>
       <c r="K24" t="n">
-        <v>1.277</v>
+        <v>1.366</v>
       </c>
       <c r="L24" t="n">
-        <v>4.351</v>
+        <v>4.604</v>
       </c>
       <c r="M24" t="n">
-        <v>0.209</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="25">
@@ -4147,34 +4363,34 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>352.748</v>
+        <v>285.074</v>
       </c>
       <c r="F25" t="n">
-        <v>0.856</v>
+        <v>0.844</v>
       </c>
       <c r="G25" t="n">
-        <v>0.104</v>
+        <v>0.375</v>
       </c>
       <c r="H25" t="n">
-        <v>23.927</v>
+        <v>25.896</v>
       </c>
       <c r="I25" t="n">
-        <v>12.01</v>
+        <v>13.01</v>
       </c>
       <c r="J25" t="n">
-        <v>0.589</v>
+        <v>0.632</v>
       </c>
       <c r="K25" t="n">
-        <v>1.462</v>
+        <v>1.325</v>
       </c>
       <c r="L25" t="n">
-        <v>4.917</v>
+        <v>4.27</v>
       </c>
       <c r="M25" t="n">
-        <v>0.192</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="26">
@@ -4192,34 +4408,34 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>394.514</v>
+        <v>310.382</v>
       </c>
       <c r="F26" t="n">
-        <v>0.752</v>
+        <v>0.779</v>
       </c>
       <c r="G26" t="n">
-        <v>0.042</v>
+        <v>0.271</v>
       </c>
       <c r="H26" t="n">
-        <v>23.854</v>
+        <v>27.688</v>
       </c>
       <c r="I26" t="n">
-        <v>11.948</v>
+        <v>13.917</v>
       </c>
       <c r="J26" t="n">
-        <v>0.495</v>
+        <v>0.626</v>
       </c>
       <c r="K26" t="n">
-        <v>1.542</v>
+        <v>1.277</v>
       </c>
       <c r="L26" t="n">
-        <v>5.347</v>
+        <v>4.351</v>
       </c>
       <c r="M26" t="n">
-        <v>0.162</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="27">
@@ -4237,34 +4453,34 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>482.772</v>
+        <v>352.748</v>
       </c>
       <c r="F27" t="n">
-        <v>0.804</v>
+        <v>0.856</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01</v>
+        <v>0.104</v>
       </c>
       <c r="H27" t="n">
-        <v>23.188</v>
+        <v>23.927</v>
       </c>
       <c r="I27" t="n">
-        <v>11.604</v>
+        <v>12.01</v>
       </c>
       <c r="J27" t="n">
-        <v>0.495</v>
+        <v>0.589</v>
       </c>
       <c r="K27" t="n">
-        <v>1.611</v>
+        <v>1.462</v>
       </c>
       <c r="L27" t="n">
-        <v>6.165</v>
+        <v>4.917</v>
       </c>
       <c r="M27" t="n">
-        <v>0.148</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="28">
@@ -4282,34 +4498,34 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>553.494</v>
+        <v>394.514</v>
       </c>
       <c r="F28" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01</v>
+        <v>0.042</v>
       </c>
       <c r="H28" t="n">
-        <v>21.719</v>
+        <v>23.854</v>
       </c>
       <c r="I28" t="n">
-        <v>10.885</v>
+        <v>11.948</v>
       </c>
       <c r="J28" t="n">
-        <v>0.41</v>
+        <v>0.495</v>
       </c>
       <c r="K28" t="n">
-        <v>1.762</v>
+        <v>1.542</v>
       </c>
       <c r="L28" t="n">
-        <v>7.569</v>
+        <v>5.347</v>
       </c>
       <c r="M28" t="n">
-        <v>0.112</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="29">
@@ -4327,34 +4543,34 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>574.405</v>
+        <v>482.772</v>
       </c>
       <c r="F29" t="n">
-        <v>0.68</v>
+        <v>0.804</v>
       </c>
       <c r="G29" t="n">
         <v>0.01</v>
       </c>
       <c r="H29" t="n">
-        <v>22.719</v>
+        <v>23.188</v>
       </c>
       <c r="I29" t="n">
-        <v>11.385</v>
+        <v>11.604</v>
       </c>
       <c r="J29" t="n">
-        <v>0.406</v>
+        <v>0.495</v>
       </c>
       <c r="K29" t="n">
-        <v>1.67</v>
+        <v>1.611</v>
       </c>
       <c r="L29" t="n">
-        <v>8.481999999999999</v>
+        <v>6.165</v>
       </c>
       <c r="M29" t="n">
-        <v>0.098</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="30">
@@ -4372,34 +4588,34 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>641.316</v>
+        <v>553.494</v>
       </c>
       <c r="F30" t="n">
-        <v>0.675</v>
+        <v>0.742</v>
       </c>
       <c r="G30" t="n">
         <v>0.01</v>
       </c>
       <c r="H30" t="n">
-        <v>20.771</v>
+        <v>21.719</v>
       </c>
       <c r="I30" t="n">
-        <v>10.406</v>
+        <v>10.885</v>
       </c>
       <c r="J30" t="n">
-        <v>0.389</v>
+        <v>0.41</v>
       </c>
       <c r="K30" t="n">
-        <v>1.764</v>
+        <v>1.762</v>
       </c>
       <c r="L30" t="n">
-        <v>8.837999999999999</v>
+        <v>7.569</v>
       </c>
       <c r="M30" t="n">
-        <v>0.083</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="31">
@@ -4417,34 +4633,34 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>641.712</v>
+        <v>574.405</v>
       </c>
       <c r="F31" t="n">
-        <v>0.647</v>
+        <v>0.68</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H31" t="n">
-        <v>19.198</v>
+        <v>22.719</v>
       </c>
       <c r="I31" t="n">
-        <v>9.646000000000001</v>
+        <v>11.385</v>
       </c>
       <c r="J31" t="n">
-        <v>0.383</v>
+        <v>0.406</v>
       </c>
       <c r="K31" t="n">
-        <v>1.646</v>
+        <v>1.67</v>
       </c>
       <c r="L31" t="n">
-        <v>9.657999999999999</v>
+        <v>8.481999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>0.078</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="32">
@@ -4462,40 +4678,40 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>686.202</v>
+        <v>641.316</v>
       </c>
       <c r="F32" t="n">
-        <v>0.55</v>
+        <v>0.675</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H32" t="n">
-        <v>20.385</v>
+        <v>20.771</v>
       </c>
       <c r="I32" t="n">
-        <v>10.229</v>
+        <v>10.406</v>
       </c>
       <c r="J32" t="n">
-        <v>0.326</v>
+        <v>0.389</v>
       </c>
       <c r="K32" t="n">
-        <v>1.67</v>
+        <v>1.764</v>
       </c>
       <c r="L32" t="n">
-        <v>10.524</v>
+        <v>8.837999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>0.061</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4504,43 +4720,43 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>274.884</v>
+        <v>641.712</v>
       </c>
       <c r="F33" t="n">
-        <v>0.766</v>
+        <v>0.647</v>
       </c>
       <c r="G33" t="n">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>30.49</v>
+        <v>19.198</v>
       </c>
       <c r="I33" t="n">
-        <v>15.302</v>
+        <v>9.646000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.616</v>
+        <v>0.383</v>
       </c>
       <c r="K33" t="n">
-        <v>1.225</v>
+        <v>1.646</v>
       </c>
       <c r="L33" t="n">
-        <v>4.265</v>
+        <v>9.657999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>0.221</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4549,37 +4765,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>288.916</v>
+        <v>686.202</v>
       </c>
       <c r="F34" t="n">
-        <v>0.767</v>
+        <v>0.55</v>
       </c>
       <c r="G34" t="n">
-        <v>0.427</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>26.323</v>
+        <v>20.385</v>
       </c>
       <c r="I34" t="n">
-        <v>13.24</v>
+        <v>10.229</v>
       </c>
       <c r="J34" t="n">
-        <v>0.619</v>
+        <v>0.326</v>
       </c>
       <c r="K34" t="n">
-        <v>1.206</v>
+        <v>1.67</v>
       </c>
       <c r="L34" t="n">
-        <v>4.393</v>
+        <v>10.524</v>
       </c>
       <c r="M34" t="n">
-        <v>0.204</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="35">
@@ -4597,34 +4813,34 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>366.031</v>
+        <v>274.884</v>
       </c>
       <c r="F35" t="n">
-        <v>0.779</v>
+        <v>0.766</v>
       </c>
       <c r="G35" t="n">
-        <v>0.417</v>
+        <v>0.448</v>
       </c>
       <c r="H35" t="n">
-        <v>26.615</v>
+        <v>30.49</v>
       </c>
       <c r="I35" t="n">
-        <v>13.396</v>
+        <v>15.302</v>
       </c>
       <c r="J35" t="n">
-        <v>0.574</v>
+        <v>0.616</v>
       </c>
       <c r="K35" t="n">
-        <v>1.334</v>
+        <v>1.225</v>
       </c>
       <c r="L35" t="n">
-        <v>5.103</v>
+        <v>4.265</v>
       </c>
       <c r="M35" t="n">
-        <v>0.194</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="36">
@@ -4642,34 +4858,34 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>421.129</v>
+        <v>288.916</v>
       </c>
       <c r="F36" t="n">
-        <v>0.823</v>
+        <v>0.767</v>
       </c>
       <c r="G36" t="n">
-        <v>0.219</v>
+        <v>0.427</v>
       </c>
       <c r="H36" t="n">
-        <v>25.49</v>
+        <v>26.323</v>
       </c>
       <c r="I36" t="n">
-        <v>12.812</v>
+        <v>13.24</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="K36" t="n">
-        <v>1.462</v>
+        <v>1.206</v>
       </c>
       <c r="L36" t="n">
-        <v>5.563</v>
+        <v>4.393</v>
       </c>
       <c r="M36" t="n">
-        <v>0.173</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="37">
@@ -4687,34 +4903,34 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>482.746</v>
+        <v>366.031</v>
       </c>
       <c r="F37" t="n">
-        <v>0.766</v>
+        <v>0.779</v>
       </c>
       <c r="G37" t="n">
-        <v>0.115</v>
+        <v>0.417</v>
       </c>
       <c r="H37" t="n">
-        <v>22.844</v>
+        <v>26.615</v>
       </c>
       <c r="I37" t="n">
-        <v>11.458</v>
+        <v>13.396</v>
       </c>
       <c r="J37" t="n">
-        <v>0.49</v>
+        <v>0.574</v>
       </c>
       <c r="K37" t="n">
-        <v>1.486</v>
+        <v>1.334</v>
       </c>
       <c r="L37" t="n">
-        <v>6.282</v>
+        <v>5.103</v>
       </c>
       <c r="M37" t="n">
-        <v>0.138</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="38">
@@ -4732,34 +4948,34 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>584.5410000000001</v>
+        <v>421.129</v>
       </c>
       <c r="F38" t="n">
-        <v>0.715</v>
+        <v>0.823</v>
       </c>
       <c r="G38" t="n">
-        <v>0.042</v>
+        <v>0.219</v>
       </c>
       <c r="H38" t="n">
-        <v>23.719</v>
+        <v>25.49</v>
       </c>
       <c r="I38" t="n">
-        <v>11.896</v>
+        <v>12.812</v>
       </c>
       <c r="J38" t="n">
-        <v>0.444</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>1.563</v>
+        <v>1.462</v>
       </c>
       <c r="L38" t="n">
-        <v>7.119</v>
+        <v>5.563</v>
       </c>
       <c r="M38" t="n">
-        <v>0.118</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="39">
@@ -4777,34 +4993,34 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>618.345</v>
+        <v>482.746</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.766</v>
       </c>
       <c r="G39" t="n">
-        <v>0.083</v>
+        <v>0.115</v>
       </c>
       <c r="H39" t="n">
-        <v>25.26</v>
+        <v>22.844</v>
       </c>
       <c r="I39" t="n">
-        <v>12.677</v>
+        <v>11.458</v>
       </c>
       <c r="J39" t="n">
-        <v>0.495</v>
+        <v>0.49</v>
       </c>
       <c r="K39" t="n">
-        <v>1.812</v>
+        <v>1.486</v>
       </c>
       <c r="L39" t="n">
-        <v>7.575</v>
+        <v>6.282</v>
       </c>
       <c r="M39" t="n">
-        <v>0.13</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="40">
@@ -4822,34 +5038,34 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>716.595</v>
+        <v>584.5410000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.595</v>
+        <v>0.715</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01</v>
+        <v>0.042</v>
       </c>
       <c r="H40" t="n">
-        <v>23.302</v>
+        <v>23.719</v>
       </c>
       <c r="I40" t="n">
-        <v>11.677</v>
+        <v>11.896</v>
       </c>
       <c r="J40" t="n">
-        <v>0.387</v>
+        <v>0.444</v>
       </c>
       <c r="K40" t="n">
-        <v>1.473</v>
+        <v>1.563</v>
       </c>
       <c r="L40" t="n">
-        <v>8.215</v>
+        <v>7.119</v>
       </c>
       <c r="M40" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="41">
@@ -4867,34 +5083,34 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>730.672</v>
+        <v>618.345</v>
       </c>
       <c r="F41" t="n">
-        <v>0.681</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0.021</v>
+        <v>0.083</v>
       </c>
       <c r="H41" t="n">
-        <v>25.646</v>
+        <v>25.26</v>
       </c>
       <c r="I41" t="n">
-        <v>12.844</v>
+        <v>12.677</v>
       </c>
       <c r="J41" t="n">
-        <v>0.417</v>
+        <v>0.495</v>
       </c>
       <c r="K41" t="n">
-        <v>1.589</v>
+        <v>1.812</v>
       </c>
       <c r="L41" t="n">
-        <v>8.754</v>
+        <v>7.575</v>
       </c>
       <c r="M41" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="42">
@@ -4912,34 +5128,34 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>801.897</v>
+        <v>716.595</v>
       </c>
       <c r="F42" t="n">
-        <v>0.589</v>
+        <v>0.595</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H42" t="n">
-        <v>27.49</v>
+        <v>23.302</v>
       </c>
       <c r="I42" t="n">
-        <v>13.771</v>
+        <v>11.677</v>
       </c>
       <c r="J42" t="n">
-        <v>0.379</v>
+        <v>0.387</v>
       </c>
       <c r="K42" t="n">
-        <v>1.531</v>
+        <v>1.473</v>
       </c>
       <c r="L42" t="n">
-        <v>8.962</v>
+        <v>8.215</v>
       </c>
       <c r="M42" t="n">
-        <v>0.075</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -4957,33 +5173,123 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>730.672</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H43" t="n">
+        <v>25.646</v>
+      </c>
+      <c r="I43" t="n">
+        <v>12.844</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.589</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8.754</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>801.897</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="I44" t="n">
+        <v>13.771</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="L44" t="n">
+        <v>8.962</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
         <v>10</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E45" t="n">
         <v>810.875</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F45" t="n">
         <v>0.616</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G45" t="n">
         <v>0.01</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H45" t="n">
         <v>28.698</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I45" t="n">
         <v>14.385</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J45" t="n">
         <v>0.419</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K45" t="n">
         <v>1.43</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L45" t="n">
         <v>8.82</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M45" t="n">
         <v>0.081</v>
       </c>
     </row>
@@ -5046,10 +5352,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="C3" t="n">
-        <v>684</v>
+        <v>814</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
